--- a/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/abr-2026.xlsx
+++ b/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/abr-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>4846.3</v>
+        <v>4901.41</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>20353.92</v>
+        <v>20417.96</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>12124.14</v>
+        <v>12162.29</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>3514.79</v>
+        <v>3529.36</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>4201.18</v>
+        <v>4183.14</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/abr-2026.xlsx
+++ b/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/abr-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC abr-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC abr-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">

--- a/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/abr-2026.xlsx
+++ b/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/abr-2026.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Hospital de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">

--- a/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/abr-2026.xlsx
+++ b/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/abr-2026.xlsx
@@ -745,7 +745,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
